--- a/GetLucky_Pro_Forma_v3.xlsx
+++ b/GetLucky_Pro_Forma_v3.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D60"/>
+  <dimension ref="B2:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -715,11 +715,11 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.15</v>
+        <v>0.169</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>16.9% — repriced 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -1289,6 +1289,21 @@
       <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Realised across 10,000 trailing entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Simulator delivery cost (% of simulator revenue)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Integration engineering, operator marketing support, platform ops</t>
         </is>
       </c>
     </row>
@@ -8592,19 +8607,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2399820</v>
       </c>
       <c r="D13" t="n">
-        <v>2399820</v>
+        <v>6399520</v>
       </c>
       <c r="E13" t="n">
-        <v>6399520</v>
+        <v>11999100</v>
       </c>
       <c r="F13" t="n">
-        <v>11999100</v>
+        <v>16663000</v>
       </c>
       <c r="G13" t="n">
-        <v>20000000</v>
+        <v>23142000</v>
       </c>
       <c r="H13" t="n">
         <v>31997600</v>
@@ -8844,13 +8859,13 @@
         <v>24000000</v>
       </c>
       <c r="F22" t="n">
-        <v>32000000</v>
+        <v>30000000</v>
       </c>
       <c r="G22" t="n">
-        <v>42000000</v>
+        <v>37000000</v>
       </c>
       <c r="H22" t="n">
-        <v>55000000</v>
+        <v>46000000</v>
       </c>
     </row>
     <row r="23">
@@ -8860,27 +8875,58 @@
         </is>
       </c>
       <c r="C23">
-        <f>SUM(C18:C22)</f>
+        <f>SUM(C18:C22)+C24</f>
         <v/>
       </c>
       <c r="D23">
-        <f>SUM(D18:D22)</f>
+        <f>SUM(D18:D22)+D24</f>
         <v/>
       </c>
       <c r="E23">
-        <f>SUM(E18:E22)</f>
+        <f>SUM(E18:E22)+E24</f>
         <v/>
       </c>
       <c r="F23">
-        <f>SUM(F18:F22)</f>
+        <f>SUM(F18:F22)+F24</f>
         <v/>
       </c>
       <c r="G23">
-        <f>SUM(G18:G22)</f>
+        <f>SUM(G18:G22)+G24</f>
         <v/>
       </c>
       <c r="H23">
-        <f>SUM(H18:H22)</f>
+        <f>SUM(H18:H22)+H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Simulator delivery</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>C13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>D13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>E13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>F13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>G13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>H13*Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -9422,7 +9468,7 @@
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headline figures from the pitch: R53.3m / R113.1m (Dec 2029) / R288.9m (2032).</t>
+          <t>Headline figures from the pitch: R47.3m / R129.9m (Dec 2029) / R288.9m (2032).</t>
         </is>
       </c>
     </row>

--- a/GetLucky_Pro_Forma_v3.xlsx
+++ b/GetLucky_Pro_Forma_v3.xlsx
@@ -704,38 +704,38 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>This round</t>
+          <t>Raise</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equity offered</t>
+          <t>Pre-money valuation (ZAR)</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.169</v>
+        <v>39000000</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>16.9% — repriced 2026-08-05</t>
+          <t>R39m pre — the round is quoted on pre-money</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Post-money (ZAR)</t>
+          <t>Post-money valuation (ZAR)</t>
         </is>
       </c>
       <c r="C9">
-        <f>C7/C8</f>
+        <f>C8+C7</f>
         <v/>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Exact: 8.0m / 15%</t>
+          <t>R47m post; equity = 8/47 = 17.0%</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -9361,7 +9361,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stake</t>
+          <t>Stake (raise / post-money)</t>
         </is>
       </c>
       <c r="C14">
@@ -9468,7 +9468,7 @@
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headline figures from the pitch: R47.3m / R129.9m (Dec 2029) / R288.9m (2032).</t>
+          <t>Headline figures from the pitch: R47m / R130m (Dec 2029) / R289m (2032).</t>
         </is>
       </c>
     </row>
@@ -9512,6 +9512,58 @@
         <is>
           <t>Insurance terms are a submission, not a bound policy.</t>
         </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MULTIPLE SENSITIVITY — the 3.0x is a choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>At 2.5x</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>Annual!E15*2.5</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>C32*$C$14/$C$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>At 3.0x (used)</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>Annual!E15*3</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>C33*$C$14/$C$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>At 3.5x</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>Annual!E15*3.5</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>C34*$C$14/$C$13</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/GetLucky_Pro_Forma_v3.xlsx
+++ b/GetLucky_Pro_Forma_v3.xlsx
@@ -711,15 +711,15 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pre-money valuation (ZAR)</t>
+          <t>Equity offered</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>39000000</v>
+        <v>0.15</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R39m pre — the round is quoted on pre-money</t>
+          <t>15% — the founder's fixed term</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
         </is>
       </c>
       <c r="C9">
-        <f>C8+C7</f>
+        <f>C7/C8</f>
         <v/>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R47m post; equity = 8/47 = 17.0%</t>
+          <t>R53.3m post; pre-money R45.3m</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headline figures from the pitch: R47m / R130m (Dec 2029) / R289m (2032).</t>
+          <t>Headline figures from the pitch: R53.3m / R130m (Dec 2029) / R289m (2032).</t>
         </is>
       </c>
     </row>
